--- a/source/Autossential.Workbook.Tests/Samples/OXML_sheets.xlsx
+++ b/source/Autossential.Workbook.Tests/Samples/OXML_sheets.xlsx
@@ -961,45 +961,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr/>
+  <x:dimension ref="A1"/>
+  <x:sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
+  <x:sheetData/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:headerFooter/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr/>
+  <x:dimension ref="A1"/>
+  <x:sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
+  <x:sheetData/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:headerFooter/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr/>
+  <x:dimension ref="A1"/>
+  <x:sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
+  <x:sheetData/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:headerFooter/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr/>
+  <x:dimension ref="A1"/>
+  <x:sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
+  <x:sheetData/>
+  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:headerFooter/>
+</x:worksheet>
 </file>